--- a/docs/downloads/gsl-indexes/pdf_citations.xlsx
+++ b/docs/downloads/gsl-indexes/pdf_citations.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="pdf_citations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Index'!$A$1:$J$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'pdf_citations'!$A$1:$J$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,28 +29,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="002E4B70"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D7EFF8"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -76,15 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,89 +435,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GSL PDF Extraction Export</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Index</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>PDF Extraction - Citations</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>gsl_pdf_extraction_master.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Conservative author-year citation matches found in the body text using citation regex patterns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Caveat</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Generated from PDF font/layout extraction; review before exam reliance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -550,3988 +451,3988 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Element Type</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Content/Text</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Author String</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Current Heading</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Book Page</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>PDF Page</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Source Line ID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Mintzberg (1994)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Mintzberg</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>THE EVOLUTION OF STRATEGY</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>P019-L007</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Chandler (1962)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Chandler</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>1962</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>THE RATIONAL APPROACH TO STRATEGY</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>P023-L015</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Buche and Dhanaraj (2019)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Buche and Dhanaraj</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PURPOSE AND STRATEGY</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I4" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>P028-L057</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Osterwalder and Pigneur (2014)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Osterwalder and Pigneur</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>RESHAPING THE VALUE PROPOSITION</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="I5" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>P029-L037</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Porter (1996)</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Porter</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>DIFFERENTIATING STRATEGY FROM TACTICS</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="I6" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>P032-L021</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Grant (2008)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Grant</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC FIT AND STRATEGIC STRETCH</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>P032-L036</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Hagel and Singer (2000)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Hagel and Singer</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Core Business Types</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>P037-L025</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Osterwalder (2013)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Osterwalder</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>The Business Model Canvas</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>P043-L034</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Kotter (1990)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Kotter</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP VERSUS MANAGEMENT</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>P053-L050</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Daft (1999)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Daft</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>1999</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>leaders</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Strategic leaders</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>P056-L021</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Tichy and Devanna (1990)</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Tichy and Devanna</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Transformational Leadership</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="I12" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>P060-L044</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Kotter (1995)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Kotter</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>effectively. This is discussed in Kotter’s eight-step change process (see module 6) with the importance</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>QUESTION 1.10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>P062-L003</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Dunphy and Stace (1994)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Dunphy and Stace</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP STYLES BASED ON THE INTENSITY OF CHANGE</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>P063-L013</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Rothschild (1993)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Rothschild</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>LIFE CYCLE STAGE</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>LEADERSHIP STYLES BASED ON ORGANISATIONAL LIFE CYCLE STAGE</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="I15" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="I15" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>P065-L007</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Kotter (1995)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Kotter</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1.8 THE ROLE OF LEADERS IN STRATEGY</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="I16" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>P067-L002</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Gleeson (2012)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Gleeson</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Why Decision Making can Vary from the ‘Rational’ in Practice</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="I17" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>P069-L023</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Dunphy (1994)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Dunphy</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>REFERENCES</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H18" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>P081-L043</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Dunphy (1994)</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Dunphy</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>REFERENCES</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>P081-L044</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Dunphy (1994)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Dunphy</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>MODULE 1</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>REFERENCES</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>P081-L046</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Fifarek and Veloso (2010)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Fifarek and Veloso</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Value added</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="I21" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="I21" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>P101-L025</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>ABS (2018)</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>ABS</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Social Factors</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="H22" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="I22" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="I22" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>P117-L032</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Bain &amp; Company (2016)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Bain &amp; Company</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Remote Environment Summary for the Luxury Goods Industry</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="I23" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>P127-L053</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Bain &amp; Company (2016)</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Bain &amp; Company</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Remote Environment Summary for the Luxury Goods Industry</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="I24" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>P128-L006</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Porter (1980)</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Porter</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>MODULE 2</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>INDUSTRY PROFITABILITY</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2.4 INDUSTRY ENVIRONMENT ANALYSIS — INDUSTRY PROFITABILITY</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="I25" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>P130-L019</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Porter (1980)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Porter</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>COMPETITIVE ADVANTAGE AND GENERIC STRATEGY</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="I26" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>P183-L036</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Porter (1980)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Porter</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>COMPETITIVE ADVANTAGE AND GENERIC STRATEGY</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="2" t="n">
         <v>183</v>
       </c>
-      <c r="I27" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="I27" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>P183-L046</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Kim and Mauborgne (2014)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Kim and Mauborgne</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Connecting Innovation and Business Strategy</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="2" t="n">
         <v>190</v>
       </c>
-      <c r="I28" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
+      <c r="I28" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>P190-L001</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Friedman (1970)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Friedman</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>1970</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>3.4 OPERATIONAL DRIVERS</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="2" t="n">
         <v>191</v>
       </c>
-      <c r="I29" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="I29" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>P191-L012</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton (1996)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>THE BALANCED SCORECARD</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="I30" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>P194-L009</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton (1996)</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>THE BALANCED SCORECARD</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="I31" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>P194-L023</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton (1996)</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>THE BALANCED SCORECARD</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="2" t="n">
         <v>194</v>
       </c>
-      <c r="I32" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>P194-L049</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton (1996)</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Kaplan and Norton</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="H33" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="I33" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="I33" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>P197-L090</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Nonaka (1994)</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Nonaka</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>MODULE 3</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Data analytics</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="2" t="n">
         <v>201</v>
       </c>
-      <c r="I34" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
+      <c r="I34" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>P201-L057</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Govindarajan and Srinivas (2013)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Govindarajan and Srinivas</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>4.3 NEW PRODUCT DEVELOPMENT (NPD)</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>226</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="2" t="n">
         <v>241</v>
       </c>
-      <c r="I35" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="I35" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>P241-L025</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>Sangiorgi and Prendiville (2019)</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Sangiorgi and Prendiville</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>COMPONENTS OF SERVICE DESIGN</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="2" t="n">
         <v>252</v>
       </c>
-      <c r="I36" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="I36" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>P252-L032</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Sawhney (2016)</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Sawhney</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>WITH TECHNOLOGY</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>EMBEDDING PRODUCTS INTO SERVICES WITH TECHNOLOGY</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>239</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="2" t="n">
         <v>254</v>
       </c>
-      <c r="I37" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
+      <c r="I37" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>P254-L046</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Sawhney (2016)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Sawhney</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>DEVELOPING PRODUCTS TO EMBED IN A SERVICE</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="2" t="n">
         <v>269</v>
       </c>
-      <c r="I38" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
+      <c r="I38" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>P269-L045</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Lasserre (2003)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Lasserre</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>MODULE 4</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Value of Mergers and Acquisitions</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="2" t="n">
         <v>288</v>
       </c>
-      <c r="I39" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
+      <c r="I39" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>P288-L010</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Evans (2013)</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Evans</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>AND MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>6.6 FURTHER IMPLICATIONS FOR LEADERSHIP AND MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>402</t>
         </is>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="2" t="n">
         <v>417</v>
       </c>
-      <c r="I40" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
+      <c r="I40" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>P417-L031</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Evans (2013)</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Evans</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>COMMON PITFALLS IN STRATEGY IMPLEMENTATION</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>403</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="2" t="n">
         <v>418</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="I41" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>P418-L030</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Trkman (2010)</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Trkman</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>2010</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Transforming Strategic Thinking into Action</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="2" t="n">
         <v>419</v>
       </c>
-      <c r="I42" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
+      <c r="I42" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>P419-L003</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Hrebiniak (2006)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Hrebiniak</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Paralysis by Analysis</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="2" t="n">
         <v>419</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="I43" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>P419-L017</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Calvert and Kurji (2012)</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Calvert and Kurji</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>CPAs and Managing the Performance of the Organisation</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="H44" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="I44" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="I44" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>P425-L012</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>(Elrod, 2012)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Elrod</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>CPAs and Managing the Performance of the Organisation</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="2" t="n">
         <v>425</v>
       </c>
-      <c r="I45" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="I45" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>P425-L026</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Vermuelen (2017)</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Vermuelen</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>MODULE 6</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>A FINAL POINT</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="2" t="n">
         <v>426</v>
       </c>
-      <c r="I46" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="I46" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>P426-L023</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Li (2018)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Li</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>421</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="2" t="n">
         <v>436</v>
       </c>
-      <c r="I47" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="I47" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>P436-L025</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Gaziulusory and Twomey (2014)</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Gaziulusory and Twomey</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Sustainability</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>424</t>
         </is>
       </c>
-      <c r="H48" s="3" t="n">
+      <c r="H48" s="2" t="n">
         <v>439</v>
       </c>
-      <c r="I48" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="I48" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>P439-L028</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>(Aarikka-Stenroos &amp; Ritala, 2017)</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Aarikka-Stenroos &amp; Ritala</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>BUSINESS ECOSYSTEMS</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>426</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="2" t="n">
         <v>441</v>
       </c>
-      <c r="I49" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="I49" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>P441-L023</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Zenger (2015)</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Zenger</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>HYPERCOMPETITION</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>426</t>
         </is>
       </c>
-      <c r="H50" s="3" t="n">
+      <c r="H50" s="2" t="n">
         <v>441</v>
       </c>
-      <c r="I50" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>P441-L045</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Moore (1996)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Moore</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>VALUE CO-CREATION IN BUSINESS ECOSYSTEMS</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>431</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="2" t="n">
         <v>446</v>
       </c>
-      <c r="I51" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="I51" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>P446-L053</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Marden (2015)</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Marden</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>HYPERDISRUPTIVE BUSINESS MODELS</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>435</t>
         </is>
       </c>
-      <c r="H52" s="3" t="n">
+      <c r="H52" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="I52" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="I52" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>P450-L025</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Peteghem (2014)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Peteghem</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>HYPERDISRUPTIVE BUSINESS MODELS</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>435</t>
         </is>
       </c>
-      <c r="H53" s="3" t="n">
+      <c r="H53" s="2" t="n">
         <v>450</v>
       </c>
-      <c r="I53" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="I53" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>P450-L025</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Whittington (1993)</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Whittington</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>1993</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>ALTERNATIVE APPROACHES TO STRATEGY</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>439</t>
         </is>
       </c>
-      <c r="H54" s="3" t="n">
+      <c r="H54" s="2" t="n">
         <v>454</v>
       </c>
-      <c r="I54" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="I54" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>P454-L025</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>McGrath and MacMillan (1995)</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>McGrath and MacMillan</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Discovery-Driven Planning</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="H55" s="3" t="n">
+      <c r="H55" s="2" t="n">
         <v>455</v>
       </c>
-      <c r="I55" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="I55" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>P455-L028</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Tripp (2013)</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Tripp</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>Design thinkingwas introduced in module 4 as a product development tool. This approach can be extended</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Design Thinking</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="H56" s="3" t="n">
+      <c r="H56" s="2" t="n">
         <v>457</v>
       </c>
-      <c r="I56" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="I56" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>P457-L012</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>CSIRO (2019)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>CSIRO</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Advanced Manufacturing</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="H57" s="3" t="n">
+      <c r="H57" s="2" t="n">
         <v>458</v>
       </c>
-      <c r="I57" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="I57" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>P458-L019</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Blank (2013)</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Blank</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Lean Start-Up</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>444</t>
         </is>
       </c>
-      <c r="H58" s="3" t="n">
+      <c r="H58" s="2" t="n">
         <v>459</v>
       </c>
-      <c r="I58" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="I58" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>P459-L021</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Brandenburger and Stuart (1996)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Brandenburger and Stuart</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>VALUE-BASED STRATEGY IN A BUSINESS ECOSYSTEM</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>449</t>
         </is>
       </c>
-      <c r="H59" s="3" t="n">
+      <c r="H59" s="2" t="n">
         <v>464</v>
       </c>
-      <c r="I59" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="I59" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>P464-L044</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>(Katz, 2018)</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Katz</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>453</t>
         </is>
       </c>
-      <c r="H60" s="3" t="n">
+      <c r="H60" s="2" t="n">
         <v>468</v>
       </c>
-      <c r="I60" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="I60" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>P468-L066</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>(Time Staff, 2000)</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Time Staff</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="H61" s="3" t="n">
+      <c r="H61" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="I61" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="I61" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>P469-L005</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>(Kopytoff, 2014)</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Kopytoff</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="H62" s="3" t="n">
+      <c r="H62" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="I62" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="I62" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>P469-L007</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>(Grove, 1996)</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Grove</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>A Contrarian Model</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="H63" s="3" t="n">
+      <c r="H63" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="I63" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="I63" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>P469-L012</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>(Smith, 2018)</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>A Contrarian Model</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n">
+      <c r="H64" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="I64" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="I64" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>P469-L023</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>(Clark, 2016)</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>Clark</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>A Contrarian Model</t>
         </is>
       </c>
-      <c r="G65" s="3" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>454</t>
         </is>
       </c>
-      <c r="H65" s="3" t="n">
+      <c r="H65" s="2" t="n">
         <v>469</v>
       </c>
-      <c r="I65" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
+      <c r="I65" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>P469-L062</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>(Ibid., 2016)</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Ibid.</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>A Contrarian Model</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="H66" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="I66" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
+      <c r="I66" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>P470-L014</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Parenthetical</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>(Dru, 1996)</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Dru</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>A Contrarian Model</t>
         </is>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H67" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="I67" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
+      <c r="I67" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>P470-L018</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Gaziulusory and Twomey (2014)</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Gaziulusory and Twomey</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Sustainability and Business Models</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>458</t>
         </is>
       </c>
-      <c r="H68" s="3" t="n">
+      <c r="H68" s="2" t="n">
         <v>473</v>
       </c>
-      <c r="I68" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
+      <c r="I68" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>P473-L032</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Oyedele (2016)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Oyedele</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Emerging National Markets and Business Models</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>459</t>
         </is>
       </c>
-      <c r="H69" s="3" t="n">
+      <c r="H69" s="2" t="n">
         <v>474</v>
       </c>
-      <c r="I69" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
+      <c r="I69" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>P474-L050</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Wit (2017)</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Wit</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>STRATEGIC INNOVATION</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="H70" s="3" t="n">
+      <c r="H70" s="2" t="n">
         <v>483</v>
       </c>
-      <c r="I70" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
+      <c r="I70" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>P483-L003</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Altringer (2013)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Altringer</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>INTRAPRENEURSHIP</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="H71" s="3" t="n">
+      <c r="H71" s="2" t="n">
         <v>484</v>
       </c>
-      <c r="I71" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="I71" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>P484-L027</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Corbett (2018)</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Corbett</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>INTRAPRENEURSHIP</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>469</t>
         </is>
       </c>
-      <c r="H72" s="3" t="n">
+      <c r="H72" s="2" t="n">
         <v>484</v>
       </c>
-      <c r="I72" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="I72" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>P484-L042</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Chesbrough and Crowther (2006)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Chesbrough and Crowther</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>2006</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Open Innovation at Philips</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>471</t>
         </is>
       </c>
-      <c r="H73" s="3" t="n">
+      <c r="H73" s="2" t="n">
         <v>486</v>
       </c>
-      <c r="I73" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
+      <c r="I73" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>P486-L008</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Girotra and Netessine (2014)</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Girotra and Netessine</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>DECISION MAKING</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="H74" s="3" t="n">
+      <c r="H74" s="2" t="n">
         <v>492</v>
       </c>
-      <c r="I74" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
+      <c r="I74" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>P492-L041</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Snabe and Trolle (2018)</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Snabe and Trolle</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>479</t>
         </is>
       </c>
-      <c r="H75" s="3" t="n">
+      <c r="H75" s="2" t="n">
         <v>494</v>
       </c>
-      <c r="I75" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
+      <c r="I75" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>P494-L006</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Christensen (1997)</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Christensen</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Managing Disruption</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="H76" s="3" t="n">
+      <c r="H76" s="2" t="n">
         <v>495</v>
       </c>
-      <c r="I76" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
+      <c r="I76" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>P495-L050</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>King and Baatartogtok (2015)</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>King and Baatartogtok</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Managing Disruption</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="H77" s="3" t="n">
+      <c r="H77" s="2" t="n">
         <v>495</v>
       </c>
-      <c r="I77" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
+      <c r="I77" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>P495-L072</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Texeira (2019)</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Texeira</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>START-UPS VERSUS INCUMBENTS</t>
         </is>
       </c>
-      <c r="G78" s="3" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>481</t>
         </is>
       </c>
-      <c r="H78" s="3" t="n">
+      <c r="H78" s="2" t="n">
         <v>496</v>
       </c>
-      <c r="I78" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
+      <c r="I78" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>P496-L032</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Texeira (2019)</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Texeira</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>(b)Analyse BuzzFeed’s relative competitive strengths and weaknesses against NYT as it has</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="H79" s="3" t="n">
+      <c r="H79" s="2" t="n">
         <v>498</v>
       </c>
-      <c r="I79" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
+      <c r="I79" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>P498-L032</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Hamel (2009)</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Hamel</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>LEADERSHIP AND MANAGEMENT DEVELOPMENT</t>
         </is>
       </c>
-      <c r="G80" s="3" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="H80" s="3" t="n">
+      <c r="H80" s="2" t="n">
         <v>498</v>
       </c>
-      <c r="I80" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
+      <c r="I80" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>P498-L045</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Yeh and Casnocha (2019)</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Yeh and Casnocha</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Informal Leadership Development</t>
         </is>
       </c>
-      <c r="G81" s="3" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>485</t>
         </is>
       </c>
-      <c r="H81" s="3" t="n">
+      <c r="H81" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="I81" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
+      <c r="I81" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>P500-L003</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>P. (2014)</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>P.</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>REFERENCES</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>487</t>
         </is>
       </c>
-      <c r="H82" s="3" t="n">
+      <c r="H82" s="2" t="n">
         <v>502</v>
       </c>
-      <c r="I82" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
+      <c r="I82" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>P502-L064</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Author-Year</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Author-Year</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>Andy (1996)</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Andy</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>MODULE 7</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>REFERENCES</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H83" s="3" t="n">
+      <c r="H83" s="2" t="n">
         <v>503</v>
       </c>
-      <c r="I83" s="3" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
+      <c r="I83" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>P503-L003</t>
         </is>
